--- a/sheets/Libetee_スーツケース増額プラン.xlsx
+++ b/sheets/Libetee_スーツケース増額プラン.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.000%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -156,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -268,6 +269,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -925,6 +941,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1005,8 +1022,8 @@
       <c r="C5" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>0.1516042653417946</v>
+      <c r="D5" s="49" t="n">
+        <v>0.001516042653417946</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>894465</v>
@@ -1014,8 +1031,8 @@
       <c r="F5" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>0.1364438388076151</v>
+      <c r="G5" s="49" t="n">
+        <v>0.001364438388076151</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>1207528</v>
@@ -1045,8 +1062,8 @@
       <c r="C6" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>0.1342722645169273</v>
+      <c r="D6" s="50" t="n">
+        <v>0.001342722645169273</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>1188310</v>
@@ -1054,8 +1071,8 @@
       <c r="F6" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="G6" s="13" t="n">
-        <v>0.1208450380652346</v>
+      <c r="G6" s="50" t="n">
+        <v>0.001208450380652346</v>
       </c>
       <c r="H6" s="14" t="n">
         <v>1782464</v>
@@ -1085,8 +1102,8 @@
       <c r="C7" s="18" t="n">
         <v>30000</v>
       </c>
-      <c r="D7" s="19" t="n">
-        <v>0.1345398239907378</v>
+      <c r="D7" s="51" t="n">
+        <v>0.001345398239907378</v>
       </c>
       <c r="E7" s="20" t="n">
         <v>1190677</v>
@@ -1094,8 +1111,8 @@
       <c r="F7" s="18" t="n">
         <v>50000</v>
       </c>
-      <c r="G7" s="19" t="n">
-        <v>0.121085841591664</v>
+      <c r="G7" s="51" t="n">
+        <v>0.00121085841591664</v>
       </c>
       <c r="H7" s="20" t="n">
         <v>1786016</v>
@@ -1125,8 +1142,8 @@
       <c r="C8" s="24" t="n">
         <v>30000</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>0.126895071306332</v>
+      <c r="D8" s="52" t="n">
+        <v>0.00126895071306332</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>1123021</v>
@@ -1134,8 +1151,8 @@
       <c r="F8" s="24" t="n">
         <v>50000</v>
       </c>
-      <c r="G8" s="25" t="n">
-        <v>0.1142055641756988</v>
+      <c r="G8" s="52" t="n">
+        <v>0.001142055641756988</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>1684532</v>
@@ -1165,8 +1182,8 @@
       <c r="C9" s="30" t="n">
         <v>30000</v>
       </c>
-      <c r="D9" s="31" t="n">
-        <v>0.3733655419830527</v>
+      <c r="D9" s="53" t="n">
+        <v>0.003733655419830527</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>3304285</v>
@@ -1174,8 +1191,8 @@
       <c r="F9" s="30" t="n">
         <v>50000</v>
       </c>
-      <c r="G9" s="31" t="n">
-        <v>0.3360289877847474</v>
+      <c r="G9" s="53" t="n">
+        <v>0.003360289877847474</v>
       </c>
       <c r="H9" s="32" t="n">
         <v>4956428</v>
@@ -1265,6 +1282,7 @@
         <v>16717450</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
@@ -1275,6 +1293,7 @@
         <v>16717450</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1326,6 +1345,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="42" t="inlineStr">
         <is>
@@ -1468,6 +1488,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="47" t="inlineStr">
         <is>
@@ -1586,6 +1607,7 @@
         <v>4956428</v>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="H8" t="inlineStr">
         <is>

--- a/sheets/Libetee_スーツケース増額プラン.xlsx
+++ b/sheets/Libetee_スーツケース増額プラン.xlsx
@@ -11,6 +11,7 @@
     <sheet name="客単価UP施策" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="グラフ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="前提と検算" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="用語解説" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +78,11 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="11">
@@ -157,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -284,6 +291,33 @@
     <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -941,7 +975,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1315,6 @@
         <v>16717450</v>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
@@ -1293,7 +1325,6 @@
         <v>16717450</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1345,7 +1376,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="42" t="inlineStr">
         <is>
@@ -1488,7 +1518,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="47" t="inlineStr">
         <is>
@@ -1607,7 +1636,6 @@
         <v>4956428</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="H8" t="inlineStr">
         <is>
@@ -1751,4 +1779,248 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>用語解説：1アクセス価値</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>お客さん1人がページに来たとき、平均していくら売上になるか</t>
+        </is>
+      </c>
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="45" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>計算式</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>1アクセス価値 ＝ 転換率 × 客単価</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="44" t="inlineStr">
+        <is>
+          <t>例（かぶり日・7月実績）</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>転換率0.73% × 客単価¥13,048 ≒ ¥95。1,000人来たら約7人が買い、売上約¥95,000 → 1人あたり¥95</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="45" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>使い方①（広告判断）</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>メタ広告のアクセス単価(約¥12)と比べる。¥12で1人連れてきて、その日の価値が¥95なら8倍で返る計算</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>使い方②（増額試算）</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>追加売上 ＝ 増やすアクセス数 × 1アクセス価値。転換率×0.8のシナリオは価値を2割引きで見積もったもの</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="45" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>1アクセス価値</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>広告単価(メタ)</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="E10" s="56" t="inlineStr">
+        <is>
+          <t>読み方</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>かぶり日（イベント×5と0）</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="n">
+        <v>95</v>
+      </c>
+      <c r="C11" s="58" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="E11" s="60" t="inlineStr">
+        <is>
+          <t>¥12仕入→¥95売上。最優先で広告を張る日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="61" t="inlineStr">
+        <is>
+          <t>ワンダフルデー</t>
+        </is>
+      </c>
+      <c r="B12" s="62" t="n">
+        <v>94</v>
+      </c>
+      <c r="C12" s="62" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="63" t="n">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="E12" s="64" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>5と0のつく日（単独）</t>
+        </is>
+      </c>
+      <c r="B13" s="66" t="n">
+        <v>61</v>
+      </c>
+      <c r="C13" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="67" t="n">
+        <v>5.083333333333333</v>
+      </c>
+      <c r="E13" s="68" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="69" t="inlineStr">
+        <is>
+          <t>マラソン通常</t>
+        </is>
+      </c>
+      <c r="B14" s="70" t="n">
+        <v>46</v>
+      </c>
+      <c r="C14" s="70" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="71" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="E14" s="72" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>平日</t>
+        </is>
+      </c>
+      <c r="B15" s="74" t="n">
+        <v>41</v>
+      </c>
+      <c r="C15" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="75" t="n">
+        <v>3.416666666666667</v>
+      </c>
+      <c r="E15" s="76" t="inlineStr">
+        <is>
+          <t>それでも3.4倍。広告を切らない理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>※スーツケースのみの価値は別掲（平日¥45／かぶり日¥110）。転換率・客単価は2026年7月実績（公式カレンダー分類）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sheets/Libetee_スーツケース増額プラン.xlsx
+++ b/sheets/Libetee_スーツケース増額プラン.xlsx
@@ -138,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -159,6 +159,50 @@
       <bottom style="thin">
         <color rgb="00BFBFBF"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -1787,20 +1831,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="54" t="inlineStr">
         <is>
-          <t>用語解説：1アクセス価値</t>
+          <t>用語解説：1アクセス価値 ／ アクセス単価の前提</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1901,7 @@
       </c>
       <c r="B6" s="55" t="inlineStr">
         <is>
-          <t>メタ広告のアクセス単価(約¥12)と比べる。¥12で1人連れてきて、その日の価値が¥95なら8倍で返る計算</t>
+          <t>アクセス単価と比べる。¥10で1人連れてきて、その日の価値が¥95なら9.5倍で返る計算</t>
         </is>
       </c>
       <c r="C6" s="45" t="n"/>
@@ -1879,142 +1923,158 @@
       <c r="D7" s="45" t="n"/>
       <c r="E7" s="45" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>★アクセス単価の統一前提</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>スーツケース ¥10/アクセス ／ ハンディファン ¥8/アクセス（社長指定・全シート共通）</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="56" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>1アクセス価値</t>
         </is>
       </c>
-      <c r="C10" s="56" t="inlineStr">
-        <is>
-          <t>広告単価(メタ)</t>
-        </is>
-      </c>
-      <c r="D10" s="56" t="inlineStr">
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>SC単価</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
         <is>
           <t>倍率</t>
         </is>
       </c>
-      <c r="E10" s="56" t="inlineStr">
+      <c r="E11" s="56" t="inlineStr">
         <is>
           <t>読み方</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="57" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>かぶり日（イベント×5と0）</t>
         </is>
       </c>
-      <c r="B11" s="58" t="n">
+      <c r="B12" s="58" t="n">
         <v>95</v>
       </c>
-      <c r="C11" s="58" t="n">
-        <v>12</v>
-      </c>
-      <c r="D11" s="59" t="n">
-        <v>7.916666666666667</v>
-      </c>
-      <c r="E11" s="60" t="inlineStr">
-        <is>
-          <t>¥12仕入→¥95売上。最優先で広告を張る日</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="C12" s="58" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="59" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>¥10仕入→¥95売上。最優先で広告を張る日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>ワンダフルデー</t>
         </is>
       </c>
-      <c r="B12" s="62" t="n">
+      <c r="B13" s="62" t="n">
         <v>94</v>
       </c>
-      <c r="C12" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="D12" s="63" t="n">
-        <v>7.833333333333333</v>
-      </c>
-      <c r="E12" s="64" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="C13" s="62" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="63" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E13" s="64" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="65" t="inlineStr">
         <is>
           <t>5と0のつく日（単独）</t>
         </is>
       </c>
-      <c r="B13" s="66" t="n">
+      <c r="B14" s="66" t="n">
         <v>61</v>
       </c>
-      <c r="C13" s="66" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="67" t="n">
-        <v>5.083333333333333</v>
-      </c>
-      <c r="E13" s="68" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="69" t="inlineStr">
+      <c r="C14" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="67" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E14" s="68" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>マラソン通常</t>
         </is>
       </c>
-      <c r="B14" s="70" t="n">
+      <c r="B15" s="70" t="n">
         <v>46</v>
       </c>
-      <c r="C14" s="70" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="71" t="n">
-        <v>3.833333333333333</v>
-      </c>
-      <c r="E14" s="72" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="73" t="inlineStr">
+      <c r="C15" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="71" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E15" s="72" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="73" t="inlineStr">
         <is>
           <t>平日</t>
         </is>
       </c>
-      <c r="B15" s="74" t="n">
+      <c r="B16" s="74" t="n">
         <v>41</v>
       </c>
-      <c r="C15" s="74" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="75" t="n">
-        <v>3.416666666666667</v>
-      </c>
-      <c r="E15" s="76" t="inlineStr">
-        <is>
-          <t>それでも3.4倍。広告を切らない理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>※スーツケースのみの価値は別掲（平日¥45／かぶり日¥110）。転換率・客単価は2026年7月実績（公式カレンダー分類）。</t>
+      <c r="C16" s="74" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="75" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E16" s="76" t="inlineStr">
+        <is>
+          <t>それでも4.1倍。広告を切らない理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>※スーツケースのみの価値：平日¥45／かぶり日¥110。ハンディファンの広告費は¥8/アクセス（据え置き）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>

--- a/sheets/Libetee_スーツケース増額プラン.xlsx
+++ b/sheets/Libetee_スーツケース増額プラン.xlsx
@@ -85,7 +85,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE2DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -362,6 +367,15 @@
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1831,255 +1845,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="54" t="inlineStr">
         <is>
-          <t>用語解説：1アクセス価値 ／ アクセス単価の前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="44" t="inlineStr">
-        <is>
-          <t>定義</t>
-        </is>
-      </c>
-      <c r="B3" s="55" t="inlineStr">
-        <is>
-          <t>お客さん1人がページに来たとき、平均していくら売上になるか</t>
-        </is>
-      </c>
-      <c r="C3" s="45" t="n"/>
-      <c r="D3" s="45" t="n"/>
-      <c r="E3" s="45" t="n"/>
+          <t>用語解説（お店にたとえた、やさしい版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="56" t="inlineStr">
+        <is>
+          <t>用語</t>
+        </is>
+      </c>
+      <c r="B3" s="56" t="inlineStr">
+        <is>
+          <t>お店で言うと</t>
+        </is>
+      </c>
+      <c r="C3" s="56" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>この店の数字(7月実績)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
-        <is>
-          <t>計算式</t>
+      <c r="A4" s="77" t="inlineStr">
+        <is>
+          <t>アクセス数</t>
         </is>
       </c>
       <c r="B4" s="55" t="inlineStr">
         <is>
-          <t>1アクセス価値 ＝ 転換率 × 客単価</t>
-        </is>
-      </c>
-      <c r="C4" s="45" t="n"/>
-      <c r="D4" s="45" t="n"/>
-      <c r="E4" s="45" t="n"/>
+          <t>お店に入ってきた人数</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="inlineStr">
+        <is>
+          <t>ページを見に来た人の数（買わない人も含む）</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="inlineStr">
+        <is>
+          <t>かぶり日 約4.2万人/日</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
-        <is>
-          <t>例（かぶり日・7月実績）</t>
+      <c r="A5" s="77" t="inlineStr">
+        <is>
+          <t>転換率</t>
         </is>
       </c>
       <c r="B5" s="55" t="inlineStr">
         <is>
-          <t>転換率0.73% × 客単価¥13,048 ≒ ¥95。1,000人来たら約7人が買い、売上約¥95,000 → 1人あたり¥95</t>
-        </is>
-      </c>
-      <c r="C5" s="45" t="n"/>
-      <c r="D5" s="45" t="n"/>
-      <c r="E5" s="45" t="n"/>
+          <t>入った人のうち買った人の割合</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>100人入店して1人買えば1%</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>かぶり日0.73%＝1,000人中7人</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
-        <is>
-          <t>使い方①（広告判断）</t>
+      <c r="A6" s="77" t="inlineStr">
+        <is>
+          <t>客単価</t>
         </is>
       </c>
       <c r="B6" s="55" t="inlineStr">
         <is>
-          <t>アクセス単価と比べる。¥10で1人連れてきて、その日の価値が¥95なら9.5倍で返る計算</t>
-        </is>
-      </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
+          <t>買った人1人の平均支払額</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>レジ1回の平均金額</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>かぶり日¥13,048</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>使い方②（増額試算）</t>
-        </is>
-      </c>
-      <c r="B7" s="55" t="inlineStr">
-        <is>
-          <t>追加売上 ＝ 増やすアクセス数 × 1アクセス価値。転換率×0.8のシナリオは価値を2割引きで見積もったもの</t>
-        </is>
-      </c>
-      <c r="C7" s="45" t="n"/>
-      <c r="D7" s="45" t="n"/>
-      <c r="E7" s="45" t="n"/>
+      <c r="A7" s="78" t="inlineStr">
+        <is>
+          <t>1アクセス価値</t>
+        </is>
+      </c>
+      <c r="B7" s="79" t="inlineStr">
+        <is>
+          <t>入店客1人あたりの平均売上</t>
+        </is>
+      </c>
+      <c r="C7" s="79" t="inlineStr">
+        <is>
+          <t>転換率×客単価。1人来店するたび平均いくら売れるか</t>
+        </is>
+      </c>
+      <c r="D7" s="79" t="inlineStr">
+        <is>
+          <t>かぶり日¥95／平日¥41</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
-        <is>
-          <t>★アクセス単価の統一前提</t>
-        </is>
-      </c>
-      <c r="B8" s="55" t="inlineStr">
-        <is>
-          <t>スーツケース ¥10/アクセス ／ ハンディファン ¥8/アクセス（社長指定・全シート共通）</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="n"/>
-      <c r="D8" s="45" t="n"/>
-      <c r="E8" s="45" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="56" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>1アクセス価値</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="inlineStr">
-        <is>
-          <t>SC単価</t>
-        </is>
-      </c>
-      <c r="D11" s="56" t="inlineStr">
+      <c r="A8" s="78" t="inlineStr">
+        <is>
+          <t>アクセス単価</t>
+        </is>
+      </c>
+      <c r="B8" s="79" t="inlineStr">
+        <is>
+          <t>1人を連れてくるチラシ代</t>
+        </is>
+      </c>
+      <c r="C8" s="79" t="inlineStr">
+        <is>
+          <t>広告費÷アクセス数</t>
+        </is>
+      </c>
+      <c r="D8" s="79" t="inlineStr">
+        <is>
+          <t>スーツケース¥10／ファン¥8（統一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>倍率</t>
         </is>
       </c>
-      <c r="E11" s="56" t="inlineStr">
-        <is>
-          <t>読み方</t>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>チラシ代の何倍売れるか</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>1アクセス価値÷アクセス単価</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>かぶり日9.5倍／平日4.1倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="77" t="inlineStr">
+        <is>
+          <t>かぶり日</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>特売日が2つ重なった日</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>お買い物マラソン×5と0のつく日</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>8/5・8/10・8/25</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="inlineStr">
-        <is>
-          <t>かぶり日（イベント×5と0）</t>
-        </is>
-      </c>
-      <c r="B12" s="58" t="n">
-        <v>95</v>
-      </c>
-      <c r="C12" s="58" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E12" s="60" t="inlineStr">
-        <is>
-          <t>¥10仕入→¥95売上。最優先で広告を張る日</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="61" t="inlineStr">
-        <is>
-          <t>ワンダフルデー</t>
-        </is>
-      </c>
-      <c r="B13" s="62" t="n">
-        <v>94</v>
-      </c>
-      <c r="C13" s="62" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="63" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E13" s="64" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="65" t="inlineStr">
-        <is>
-          <t>5と0のつく日（単独）</t>
-        </is>
-      </c>
-      <c r="B14" s="66" t="n">
-        <v>61</v>
-      </c>
-      <c r="C14" s="66" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="67" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E14" s="68" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="69" t="inlineStr">
-        <is>
-          <t>マラソン通常</t>
-        </is>
-      </c>
-      <c r="B15" s="70" t="n">
-        <v>46</v>
-      </c>
-      <c r="C15" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" s="71" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E15" s="72" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>平日</t>
-        </is>
-      </c>
-      <c r="B16" s="74" t="n">
-        <v>41</v>
-      </c>
-      <c r="C16" s="74" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="75" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E16" s="76" t="inlineStr">
-        <is>
-          <t>それでも4.1倍。広告を切らない理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>※スーツケースのみの価値：平日¥45／かぶり日¥110。ハンディファンの広告費は¥8/アクセス（据え置き）。</t>
-        </is>
-      </c>
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>商売の流れ</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>広告費を払う(¥10で1人) → お客さんが来る(アクセス) → 一部が買う(転換率) → 売上(客単価)</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>かぶり日の例</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>¥10×1,000人=広告費¥1万 → 1,000人来店 → 7人購入 → 売上¥95,000（＝9.5倍）。平日は同じ¥1万で¥41,000（4.1倍）</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="n"/>
+      <c r="D13" s="45" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B5:E5"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
